--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-16.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-16.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_trading_lay0x1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_2B593D9757C9E97713793B1159C480714891E657" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{761B216C-A569-4554-AE0D-2A15529FAC7B}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_2B593D9757C9E97713793B1159C480714891E657" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{877B40F2-EC53-4FBF-9796-2BC6F5AECFEC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,7 +223,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -279,7 +279,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -295,6 +295,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -604,10 +608,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,7 +652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -673,18 +680,22 @@
       <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="J2">
-        <v>1</v>
+      <c r="J2" t="str">
+        <f>IF(M2=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(J2=1,0.935/(F2-1)*H2,-H2)</f>
+        <f>IF(M2=1,0.935/(F2-1)*H2,-H2)</f>
         <v>5.666666666666667</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
       </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -712,18 +723,22 @@
       <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="J3">
-        <v>1</v>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J10" si="0">IF(M3=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
       </c>
       <c r="K3" s="2">
-        <f t="shared" ref="K3:K10" si="0">IF(J3=1,0.935/(F3-1)*H3,-H3)</f>
+        <f t="shared" ref="K3:K10" si="1">IF(M3=1,0.935/(F3-1)*H3,-H3)</f>
         <v>17</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
       </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -751,18 +766,22 @@
       <c r="I4" t="s">
         <v>31</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14.384615384615385</v>
       </c>
       <c r="L4" t="s">
         <v>19</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -790,18 +809,22 @@
       <c r="I5" t="s">
         <v>37</v>
       </c>
-      <c r="J5">
-        <v>1</v>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15.583333333333336</v>
       </c>
       <c r="L5" t="s">
         <v>19</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -829,18 +852,22 @@
       <c r="I6" t="s">
         <v>43</v>
       </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.35</v>
       </c>
       <c r="L6" t="s">
         <v>19</v>
       </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -868,18 +895,22 @@
       <c r="I7" t="s">
         <v>48</v>
       </c>
-      <c r="J7">
-        <v>1</v>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.9259259259259256</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -907,18 +938,22 @@
       <c r="I8" t="s">
         <v>51</v>
       </c>
-      <c r="J8">
-        <v>1</v>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.3428571428571425</v>
       </c>
       <c r="L8" t="s">
         <v>19</v>
       </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -946,18 +981,22 @@
       <c r="I9" t="s">
         <v>56</v>
       </c>
-      <c r="J9">
-        <v>1</v>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11.333333333333334</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
       </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -985,15 +1024,19 @@
       <c r="I10" t="s">
         <v>51</v>
       </c>
-      <c r="J10">
-        <v>1</v>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.3428571428571425</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-16.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_2B593D9757C9E97713793B1159C480714891E657" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{877B40F2-EC53-4FBF-9796-2BC6F5AECFEC}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_2B593D9757C9E97713793B1159C480714891E657" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC92E9E4-ACE1-419F-9F1F-928DB4E2D70C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -684,10 +684,7 @@
         <f>IF(M2=1,"GREEN", "RED")</f>
         <v>GREEN</v>
       </c>
-      <c r="K2" s="2">
-        <f>IF(M2=1,0.935/(F2-1)*H2,-H2)</f>
-        <v>5.666666666666667</v>
-      </c>
+      <c r="K2" s="2"/>
       <c r="L2" t="s">
         <v>19</v>
       </c>
@@ -727,10 +724,7 @@
         <f t="shared" ref="J3:J10" si="0">IF(M3=1,"GREEN", "RED")</f>
         <v>GREEN</v>
       </c>
-      <c r="K3" s="2">
-        <f t="shared" ref="K3:K10" si="1">IF(M3=1,0.935/(F3-1)*H3,-H3)</f>
-        <v>17</v>
-      </c>
+      <c r="K3" s="2"/>
       <c r="L3" t="s">
         <v>19</v>
       </c>
@@ -770,10 +764,7 @@
         <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K4" s="2">
-        <f t="shared" si="1"/>
-        <v>14.384615384615385</v>
-      </c>
+      <c r="K4" s="2"/>
       <c r="L4" t="s">
         <v>19</v>
       </c>
@@ -813,10 +804,7 @@
         <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K5" s="2">
-        <f t="shared" si="1"/>
-        <v>15.583333333333336</v>
-      </c>
+      <c r="K5" s="2"/>
       <c r="L5" t="s">
         <v>19</v>
       </c>
@@ -854,17 +842,14 @@
       </c>
       <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K6" s="2">
-        <f t="shared" si="1"/>
-        <v>9.35</v>
-      </c>
+        <v>RED</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" t="s">
         <v>19</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -899,10 +884,7 @@
         <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K7" s="2">
-        <f t="shared" si="1"/>
-        <v>6.9259259259259256</v>
-      </c>
+      <c r="K7" s="2"/>
       <c r="L7" t="s">
         <v>19</v>
       </c>
@@ -942,10 +924,7 @@
         <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K8" s="2">
-        <f t="shared" si="1"/>
-        <v>5.3428571428571425</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" t="s">
         <v>19</v>
       </c>
@@ -985,10 +964,7 @@
         <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K9" s="2">
-        <f t="shared" si="1"/>
-        <v>11.333333333333334</v>
-      </c>
+      <c r="K9" s="2"/>
       <c r="L9" t="s">
         <v>19</v>
       </c>
@@ -1028,10 +1004,7 @@
         <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K10" s="2">
-        <f t="shared" si="1"/>
-        <v>5.3428571428571425</v>
-      </c>
+      <c r="K10" s="2"/>
       <c r="L10" t="s">
         <v>19</v>
       </c>

--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-16.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-16.xlsx
@@ -295,10 +295,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
